--- a/data/assets_yfinance.xlsx
+++ b/data/assets_yfinance.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D424"/>
+  <dimension ref="A1:C425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,6 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -466,7 +461,6 @@
       <c r="C2" t="n">
         <v>0.3147319853305817</v>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -478,7 +472,6 @@
       <c r="C3" t="n">
         <v>0.3080359995365143</v>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -490,7 +483,6 @@
       <c r="C4" t="n">
         <v>0.2991069853305817</v>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -502,7 +494,6 @@
       <c r="C5" t="n">
         <v>0.3571430146694183</v>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -514,7 +505,6 @@
       <c r="C6" t="n">
         <v>0.3549109995365143</v>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -526,7 +516,6 @@
       <c r="C7" t="n">
         <v>0.3694199919700623</v>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -538,7 +527,6 @@
       <c r="C8" t="n">
         <v>0.3973209857940674</v>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -550,7 +538,6 @@
       <c r="C9" t="n">
         <v>0.375</v>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -562,7 +549,6 @@
       <c r="C10" t="n">
         <v>0.3258930146694183</v>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -574,7 +560,6 @@
       <c r="C11" t="n">
         <v>0.2633930146694183</v>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -586,7 +571,6 @@
       <c r="C12" t="n">
         <v>0.2723209857940674</v>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -598,7 +582,6 @@
       <c r="C13" t="n">
         <v>0.3325890004634857</v>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -610,7 +593,6 @@
       <c r="C14" t="n">
         <v>0.3816959857940674</v>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -622,7 +604,6 @@
       <c r="C15" t="n">
         <v>0.4955359995365143</v>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -634,7 +615,6 @@
       <c r="C16" t="n">
         <v>0.5089290142059326</v>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -646,7 +626,6 @@
       <c r="C17" t="n">
         <v>0.6071429848670959</v>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -658,7 +637,6 @@
       <c r="C18" t="n">
         <v>0.4285709857940674</v>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -670,7 +648,6 @@
       <c r="C19" t="n">
         <v>0.4196430146694183</v>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -682,7 +659,6 @@
       <c r="C20" t="n">
         <v>0.3772319853305817</v>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -694,7 +670,6 @@
       <c r="C21" t="n">
         <v>0.4107140004634857</v>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -706,7 +681,6 @@
       <c r="C22" t="n">
         <v>0.4709819853305817</v>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -718,7 +692,6 @@
       <c r="C23" t="n">
         <v>0.4397319853305817</v>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -730,7 +703,6 @@
       <c r="C24" t="n">
         <v>0.4575890004634857</v>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -742,7 +714,6 @@
       <c r="C25" t="n">
         <v>0.453125</v>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -754,7 +725,6 @@
       <c r="C26" t="n">
         <v>0.4977680146694183</v>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -766,7 +736,6 @@
       <c r="C27" t="n">
         <v>0.578125</v>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -778,7 +747,6 @@
       <c r="C28" t="n">
         <v>0.6049110293388367</v>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -790,7 +758,6 @@
       <c r="C29" t="n">
         <v>0.5111610293388367</v>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -802,7 +769,6 @@
       <c r="C30" t="n">
         <v>0.5357139706611633</v>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -814,7 +780,6 @@
       <c r="C31" t="n">
         <v>0.5111610293388367</v>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -826,7 +791,6 @@
       <c r="C32" t="n">
         <v>0.4285709857940674</v>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -838,7 +802,6 @@
       <c r="C33" t="n">
         <v>0.4174109995365143</v>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -850,7 +813,6 @@
       <c r="C34" t="n">
         <v>0.4129459857940674</v>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -862,7 +824,6 @@
       <c r="C35" t="n">
         <v>0.3995540142059326</v>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -874,7 +835,6 @@
       <c r="C36" t="n">
         <v>0.46875</v>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -886,7 +846,6 @@
       <c r="C37" t="n">
         <v>0.5111610293388367</v>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -898,7 +857,6 @@
       <c r="C38" t="n">
         <v>0.53125</v>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -910,7 +868,6 @@
       <c r="C39" t="n">
         <v>0.5290179848670959</v>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -922,7 +879,6 @@
       <c r="C40" t="n">
         <v>0.4732140004634857</v>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -934,7 +890,6 @@
       <c r="C41" t="n">
         <v>0.4575890004634857</v>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -946,7 +901,6 @@
       <c r="C42" t="n">
         <v>0.4575890004634857</v>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -958,7 +912,6 @@
       <c r="C43" t="n">
         <v>0.5044639706611633</v>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -970,7 +923,6 @@
       <c r="C44" t="n">
         <v>0.3482140004634857</v>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -982,7 +934,6 @@
       <c r="C45" t="n">
         <v>0.2522319853305817</v>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -994,7 +945,6 @@
       <c r="C46" t="n">
         <v>0.2366070002317429</v>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1006,7 +956,6 @@
       <c r="C47" t="n">
         <v>0.203125</v>
       </c>
-      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -1018,7 +967,6 @@
       <c r="C48" t="n">
         <v>0.2745540142059326</v>
       </c>
-      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -1030,7 +978,6 @@
       <c r="C49" t="n">
         <v>0.2857140004634857</v>
       </c>
-      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1042,7 +989,6 @@
       <c r="C50" t="n">
         <v>0.2633930146694183</v>
       </c>
-      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1054,7 +1000,6 @@
       <c r="C51" t="n">
         <v>0.2946430146694183</v>
       </c>
-      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1066,7 +1011,6 @@
       <c r="C52" t="n">
         <v>0.328125</v>
       </c>
-      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -1078,7 +1022,6 @@
       <c r="C53" t="n">
         <v>0.2879459857940674</v>
       </c>
-      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1090,7 +1033,6 @@
       <c r="C54" t="n">
         <v>0.2678569853305817</v>
       </c>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -1102,7 +1044,6 @@
       <c r="C55" t="n">
         <v>0.2544640004634857</v>
       </c>
-      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -1114,7 +1055,6 @@
       <c r="C56" t="n">
         <v>0.2354909926652908</v>
       </c>
-      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -1126,7 +1066,6 @@
       <c r="C57" t="n">
         <v>0.3002229928970337</v>
       </c>
-      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -1138,7 +1077,6 @@
       <c r="C58" t="n">
         <v>0.3158479928970337</v>
       </c>
-      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -1150,7 +1088,6 @@
       <c r="C59" t="n">
         <v>0.3002229928970337</v>
       </c>
-      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -1162,7 +1099,6 @@
       <c r="C60" t="n">
         <v>0.3828130066394806</v>
       </c>
-      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -1174,7 +1110,6 @@
       <c r="C61" t="n">
         <v>0.3303569853305817</v>
       </c>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -1186,7 +1121,6 @@
       <c r="C62" t="n">
         <v>0.3470979928970337</v>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -1198,7 +1132,6 @@
       <c r="C63" t="n">
         <v>0.3638390004634857</v>
       </c>
-      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -1210,7 +1143,6 @@
       <c r="C64" t="n">
         <v>0.3549109995365143</v>
       </c>
-      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -1222,7 +1154,6 @@
       <c r="C65" t="n">
         <v>0.3169640004634857</v>
       </c>
-      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -1234,7 +1165,6 @@
       <c r="C66" t="n">
         <v>0.3415180146694183</v>
       </c>
-      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -1246,7 +1176,6 @@
       <c r="C67" t="n">
         <v>0.373883992433548</v>
       </c>
-      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -1258,7 +1187,6 @@
       <c r="C68" t="n">
         <v>0.4151790142059326</v>
       </c>
-      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -1270,7 +1198,6 @@
       <c r="C69" t="n">
         <v>0.4006699919700623</v>
       </c>
-      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -1282,7 +1209,6 @@
       <c r="C70" t="n">
         <v>0.3839290142059326</v>
       </c>
-      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -1294,7 +1220,6 @@
       <c r="C71" t="n">
         <v>0.3370540142059326</v>
       </c>
-      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -1306,7 +1231,6 @@
       <c r="C72" t="n">
         <v>0.327008992433548</v>
       </c>
-      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -1318,7 +1242,6 @@
       <c r="C73" t="n">
         <v>0.3392859995365143</v>
       </c>
-      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -1330,7 +1253,6 @@
       <c r="C74" t="n">
         <v>0.2879459857940674</v>
       </c>
-      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -1342,7 +1264,6 @@
       <c r="C75" t="n">
         <v>0.2455359995365143</v>
       </c>
-      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -1354,7 +1275,6 @@
       <c r="C76" t="n">
         <v>0.2466520071029663</v>
       </c>
-      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -1366,7 +1286,6 @@
       <c r="C77" t="n">
         <v>0.2243299931287766</v>
       </c>
-      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -1378,7 +1297,6 @@
       <c r="C78" t="n">
         <v>0.2176340073347092</v>
       </c>
-      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -1390,7 +1308,6 @@
       <c r="C79" t="n">
         <v>0.2310270071029663</v>
       </c>
-      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -1402,7 +1319,6 @@
       <c r="C80" t="n">
         <v>0.1886159926652908</v>
       </c>
-      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -1414,7 +1330,6 @@
       <c r="C81" t="n">
         <v>0.1964289993047714</v>
       </c>
-      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -1426,7 +1341,6 @@
       <c r="C82" t="n">
         <v>0.2154020071029663</v>
       </c>
-      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -1438,7 +1352,6 @@
       <c r="C83" t="n">
         <v>0.1964289993047714</v>
       </c>
-      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -1450,7 +1363,6 @@
       <c r="C84" t="n">
         <v>0.2087049931287766</v>
       </c>
-      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -1462,7 +1374,6 @@
       <c r="C85" t="n">
         <v>0.2154020071029663</v>
       </c>
-      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -1474,7 +1385,6 @@
       <c r="C86" t="n">
         <v>0.1886159926652908</v>
       </c>
-      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -1486,7 +1396,6 @@
       <c r="C87" t="n">
         <v>0.1506700068712234</v>
       </c>
-      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -1498,7 +1407,6 @@
       <c r="C88" t="n">
         <v>0.1473210006952286</v>
       </c>
-      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -1510,7 +1418,6 @@
       <c r="C89" t="n">
         <v>0.1573659926652908</v>
       </c>
-      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -1522,7 +1429,6 @@
       <c r="C90" t="n">
         <v>0.1506700068712234</v>
       </c>
-      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -1534,7 +1440,6 @@
       <c r="C91" t="n">
         <v>0.1517859995365143</v>
       </c>
-      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -1546,7 +1451,6 @@
       <c r="C92" t="n">
         <v>0.1244420036673546</v>
       </c>
-      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -1558,7 +1462,6 @@
       <c r="C93" t="n">
         <v>0.1573659926652908</v>
       </c>
-      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -1570,7 +1473,6 @@
       <c r="C94" t="n">
         <v>0.1964289993047714</v>
       </c>
-      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -1582,7 +1484,6 @@
       <c r="C95" t="n">
         <v>0.1936379969120026</v>
       </c>
-      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -1594,7 +1495,6 @@
       <c r="C96" t="n">
         <v>0.156808003783226</v>
       </c>
-      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -1606,7 +1506,6 @@
       <c r="C97" t="n">
         <v>0.1579239964485168</v>
       </c>
-      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -1618,7 +1517,6 @@
       <c r="C98" t="n">
         <v>0.1216519996523857</v>
       </c>
-      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -1630,7 +1528,6 @@
       <c r="C99" t="n">
         <v>0.1651789993047714</v>
       </c>
-      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -1642,7 +1539,6 @@
       <c r="C100" t="n">
         <v>0.2103790044784546</v>
       </c>
-      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -1654,7 +1550,6 @@
       <c r="C101" t="n">
         <v>0.2449779957532883</v>
       </c>
-      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -1666,7 +1561,6 @@
       <c r="C102" t="n">
         <v>0.2455359995365143</v>
       </c>
-      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -1678,7 +1572,6 @@
       <c r="C103" t="n">
         <v>0.2366070002317429</v>
       </c>
-      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -1690,7 +1583,6 @@
       <c r="C104" t="n">
         <v>0.2578130066394806</v>
       </c>
-      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -1702,7 +1594,6 @@
       <c r="C105" t="n">
         <v>0.3058040142059326</v>
       </c>
-      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -1714,7 +1605,6 @@
       <c r="C106" t="n">
         <v>0.280133992433548</v>
       </c>
-      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -1726,7 +1616,6 @@
       <c r="C107" t="n">
         <v>0.328125</v>
       </c>
-      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -1738,7 +1627,6 @@
       <c r="C108" t="n">
         <v>0.3348209857940674</v>
       </c>
-      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -1750,7 +1638,6 @@
       <c r="C109" t="n">
         <v>0.2857140004634857</v>
       </c>
-      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -1762,7 +1649,6 @@
       <c r="C110" t="n">
         <v>0.376116007566452</v>
       </c>
-      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -1774,7 +1660,6 @@
       <c r="C111" t="n">
         <v>0.3722099959850311</v>
       </c>
-      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -1786,7 +1671,6 @@
       <c r="C112" t="n">
         <v>0.3108260035514832</v>
       </c>
-      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -1798,7 +1682,6 @@
       <c r="C113" t="n">
         <v>0.3219870030879974</v>
       </c>
-      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -1810,7 +1693,6 @@
       <c r="C114" t="n">
         <v>0.4112719893455505</v>
       </c>
-      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -1822,7 +1704,6 @@
       <c r="C115" t="n">
         <v>0.4017859995365143</v>
       </c>
-      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -1834,7 +1715,6 @@
       <c r="C116" t="n">
         <v>0.4135040044784546</v>
       </c>
-      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -1846,7 +1726,6 @@
       <c r="C117" t="n">
         <v>0.4966520071029663</v>
       </c>
-      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -1858,7 +1737,6 @@
       <c r="C118" t="n">
         <v>0.5982139706611633</v>
       </c>
-      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -1870,7 +1748,6 @@
       <c r="C119" t="n">
         <v>0.5546879768371582</v>
       </c>
-      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -1882,7 +1759,6 @@
       <c r="C120" t="n">
         <v>0.7142860293388367</v>
       </c>
-      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -1894,7 +1770,6 @@
       <c r="C121" t="n">
         <v>0.9017860293388367</v>
       </c>
-      <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -1906,7 +1781,6 @@
       <c r="C122" t="n">
         <v>0.9363840222358704</v>
       </c>
-      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -1918,7 +1792,6 @@
       <c r="C123" t="n">
         <v>0.9285709857940674</v>
       </c>
-      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -1930,7 +1803,6 @@
       <c r="C124" t="n">
         <v>1.058593988418579</v>
       </c>
-      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -1942,7 +1814,6 @@
       <c r="C125" t="n">
         <v>1.209820985794067</v>
       </c>
-      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -1954,7 +1825,6 @@
       <c r="C126" t="n">
         <v>1.114954948425293</v>
       </c>
-      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -1966,7 +1836,6 @@
       <c r="C127" t="n">
         <v>0.7299110293388367</v>
       </c>
-      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -1978,7 +1847,6 @@
       <c r="C128" t="n">
         <v>0.9308040142059326</v>
       </c>
-      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -1990,7 +1858,6 @@
       <c r="C129" t="n">
         <v>0.8984379768371582</v>
       </c>
-      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -2002,7 +1869,6 @@
       <c r="C130" t="n">
         <v>1.094866037368774</v>
       </c>
-      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -2014,7 +1880,6 @@
       <c r="C131" t="n">
         <v>0.4765630066394806</v>
       </c>
-      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -2026,7 +1891,6 @@
       <c r="C132" t="n">
         <v>0.3470979928970337</v>
       </c>
-      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -2038,7 +1902,6 @@
       <c r="C133" t="n">
         <v>0.3035709857940674</v>
       </c>
-      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -2050,7 +1913,6 @@
       <c r="C134" t="n">
         <v>0.265625</v>
       </c>
-      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -2062,7 +1924,6 @@
       <c r="C135" t="n">
         <v>0.3694199919700623</v>
       </c>
-      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -2074,7 +1935,6 @@
       <c r="C136" t="n">
         <v>0.3180800080299377</v>
       </c>
-      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -2086,7 +1946,6 @@
       <c r="C137" t="n">
         <v>0.394463986158371</v>
       </c>
-      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -2098,7 +1957,6 @@
       <c r="C138" t="n">
         <v>0.4537500143051147</v>
       </c>
-      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -2110,7 +1968,6 @@
       <c r="C139" t="n">
         <v>0.3594639897346497</v>
       </c>
-      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -2122,7 +1979,6 @@
       <c r="C140" t="n">
         <v>0.4221430122852325</v>
       </c>
-      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -2134,7 +1990,6 @@
       <c r="C141" t="n">
         <v>0.339464008808136</v>
       </c>
-      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -2146,7 +2001,6 @@
       <c r="C142" t="n">
         <v>0.3303569853305817</v>
       </c>
-      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -2158,7 +2012,6 @@
       <c r="C143" t="n">
         <v>0.2766070067882538</v>
       </c>
-      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -2170,7 +2023,6 @@
       <c r="C144" t="n">
         <v>0.3151789903640747</v>
       </c>
-      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -2182,7 +2034,6 @@
       <c r="C145" t="n">
         <v>0.3760710060596466</v>
       </c>
-      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -2194,7 +2045,6 @@
       <c r="C146" t="n">
         <v>0.393750011920929</v>
       </c>
-      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -2206,7 +2056,6 @@
       <c r="C147" t="n">
         <v>0.4346430003643036</v>
       </c>
-      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -2218,7 +2067,6 @@
       <c r="C148" t="n">
         <v>0.3916069865226746</v>
       </c>
-      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -2230,7 +2078,6 @@
       <c r="C149" t="n">
         <v>0.4174999892711639</v>
       </c>
-      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -2242,7 +2089,6 @@
       <c r="C150" t="n">
         <v>0.4337500035762787</v>
       </c>
-      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -2254,7 +2100,6 @@
       <c r="C151" t="n">
         <v>0.4176790118217468</v>
       </c>
-      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -2266,7 +2111,6 @@
       <c r="C152" t="n">
         <v>0.3162499964237213</v>
       </c>
-      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -2278,7 +2122,6 @@
       <c r="C153" t="n">
         <v>0.2698209881782532</v>
       </c>
-      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -2290,7 +2133,6 @@
       <c r="C154" t="n">
         <v>0.2587499916553497</v>
       </c>
-      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -2302,7 +2144,6 @@
       <c r="C155" t="n">
         <v>0.2605359852313995</v>
       </c>
-      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -2314,7 +2155,6 @@
       <c r="C156" t="n">
         <v>0.2846429944038391</v>
       </c>
-      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -2326,7 +2166,6 @@
       <c r="C157" t="n">
         <v>0.2839289903640747</v>
       </c>
-      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -2338,7 +2177,6 @@
       <c r="C158" t="n">
         <v>0.256428986787796</v>
       </c>
-      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -2350,7 +2188,6 @@
       <c r="C159" t="n">
         <v>0.2573210000991821</v>
       </c>
-      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -2362,7 +2199,6 @@
       <c r="C160" t="n">
         <v>0.2680360078811646</v>
       </c>
-      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -2374,7 +2210,6 @@
       <c r="C161" t="n">
         <v>0.2535710036754608</v>
       </c>
-      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -2386,7 +2221,6 @@
       <c r="C162" t="n">
         <v>0.2544640004634857</v>
       </c>
-      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -2398,7 +2232,6 @@
       <c r="C163" t="n">
         <v>0.3232139945030212</v>
       </c>
-      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -2410,7 +2243,6 @@
       <c r="C164" t="n">
         <v>0.3369640111923218</v>
       </c>
-      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -2422,7 +2254,6 @@
       <c r="C165" t="n">
         <v>0.375</v>
       </c>
-      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -2434,7 +2265,6 @@
       <c r="C166" t="n">
         <v>0.4046429991722107</v>
       </c>
-      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -2446,7 +2276,6 @@
       <c r="C167" t="n">
         <v>0.3698210120201111</v>
       </c>
-      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -2458,7 +2287,6 @@
       <c r="C168" t="n">
         <v>0.4076789915561676</v>
       </c>
-      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -2470,7 +2298,6 @@
       <c r="C169" t="n">
         <v>0.3757140040397644</v>
       </c>
-      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -2482,7 +2309,6 @@
       <c r="C170" t="n">
         <v>0.3848209977149963</v>
       </c>
-      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -2494,7 +2320,6 @@
       <c r="C171" t="n">
         <v>0.4010710120201111</v>
       </c>
-      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -2506,7 +2331,6 @@
       <c r="C172" t="n">
         <v>0.4303570091724396</v>
       </c>
-      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -2518,7 +2342,6 @@
       <c r="C173" t="n">
         <v>0.4801790118217468</v>
       </c>
-      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -2530,7 +2353,6 @@
       <c r="C174" t="n">
         <v>0.4642859995365143</v>
       </c>
-      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -2542,7 +2364,6 @@
       <c r="C175" t="n">
         <v>0.4962500035762787</v>
       </c>
-      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -2554,7 +2375,6 @@
       <c r="C176" t="n">
         <v>0.5732139945030212</v>
       </c>
-      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -2566,7 +2386,6 @@
       <c r="C177" t="n">
         <v>0.5567860007286072</v>
       </c>
-      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -2578,7 +2397,6 @@
       <c r="C178" t="n">
         <v>0.612500011920929</v>
       </c>
-      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -2590,7 +2408,6 @@
       <c r="C179" t="n">
         <v>0.6985710263252258</v>
       </c>
-      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -2602,7 +2419,6 @@
       <c r="C180" t="n">
         <v>0.9375</v>
       </c>
-      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -2614,7 +2430,6 @@
       <c r="C181" t="n">
         <v>1.210536003112793</v>
       </c>
-      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -2626,7 +2441,6 @@
       <c r="C182" t="n">
         <v>1.15678596496582</v>
       </c>
-      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -2638,7 +2452,6 @@
       <c r="C183" t="n">
         <v>1.375892996788025</v>
       </c>
-      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -2650,7 +2463,6 @@
       <c r="C184" t="n">
         <v>1.606786012649536</v>
       </c>
-      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -2662,7 +2474,6 @@
       <c r="C185" t="n">
         <v>1.503214001655579</v>
       </c>
-      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -2674,7 +2485,6 @@
       <c r="C186" t="n">
         <v>1.293213963508606</v>
       </c>
-      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -2686,7 +2496,6 @@
       <c r="C187" t="n">
         <v>1.424643039703369</v>
       </c>
-      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -2698,7 +2507,6 @@
       <c r="C188" t="n">
         <v>1.315356969833374</v>
       </c>
-      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -2710,7 +2518,6 @@
       <c r="C189" t="n">
         <v>1.520357012748718</v>
       </c>
-      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -2722,7 +2529,6 @@
       <c r="C190" t="n">
         <v>1.678570985794067</v>
       </c>
-      <c r="D190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -2734,7 +2540,6 @@
       <c r="C191" t="n">
         <v>1.934285998344421</v>
       </c>
-      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -2746,7 +2551,6 @@
       <c r="C192" t="n">
         <v>2.044286012649536</v>
       </c>
-      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -2758,7 +2562,6 @@
       <c r="C193" t="n">
         <v>2.462500095367432</v>
       </c>
-      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -2770,7 +2573,6 @@
       <c r="C194" t="n">
         <v>2.585000038146973</v>
       </c>
-      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -2782,7 +2584,6 @@
       <c r="C195" t="n">
         <v>2.676785945892334</v>
       </c>
-      <c r="D195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -2794,7 +2595,6 @@
       <c r="C196" t="n">
         <v>2.458570957183838</v>
       </c>
-      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -2806,7 +2606,6 @@
       <c r="C197" t="n">
         <v>2.273929119110107</v>
       </c>
-      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -2818,7 +2617,6 @@
       <c r="C198" t="n">
         <v>2.527499914169312</v>
       </c>
-      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -2830,7 +2628,6 @@
       <c r="C199" t="n">
         <v>2.137500047683716</v>
       </c>
-      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -2842,7 +2639,6 @@
       <c r="C200" t="n">
         <v>2.054286003112793</v>
       </c>
-      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -2854,7 +2650,6 @@
       <c r="C201" t="n">
         <v>2.400713920593262</v>
       </c>
-      <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -2866,7 +2661,6 @@
       <c r="C202" t="n">
         <v>2.445713996887207</v>
       </c>
-      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -2878,7 +2672,6 @@
       <c r="C203" t="n">
         <v>2.682142972946167</v>
       </c>
-      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -2890,7 +2683,6 @@
       <c r="C204" t="n">
         <v>2.896429061889648</v>
       </c>
-      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -2902,7 +2694,6 @@
       <c r="C205" t="n">
         <v>3.278570890426636</v>
       </c>
-      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -2914,7 +2705,6 @@
       <c r="C206" t="n">
         <v>3.081785917282104</v>
       </c>
-      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -2926,7 +2716,6 @@
       <c r="C207" t="n">
         <v>3.07964301109314</v>
       </c>
-      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -2938,7 +2727,6 @@
       <c r="C208" t="n">
         <v>3.001070976257324</v>
       </c>
-      <c r="D208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -2950,7 +2738,6 @@
       <c r="C209" t="n">
         <v>3.362143039703369</v>
       </c>
-      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -2962,7 +2749,6 @@
       <c r="C210" t="n">
         <v>3.556786060333252</v>
       </c>
-      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -2974,7 +2760,6 @@
       <c r="C211" t="n">
         <v>4.324999809265137</v>
       </c>
-      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -2986,7 +2771,6 @@
       <c r="C212" t="n">
         <v>4.323214054107666</v>
       </c>
-      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -2998,7 +2782,6 @@
       <c r="C213" t="n">
         <v>4.772857189178467</v>
       </c>
-      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -3010,7 +2793,6 @@
       <c r="C214" t="n">
         <v>4.997857093811035</v>
       </c>
-      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -3022,7 +2804,6 @@
       <c r="C215" t="n">
         <v>5.522500038146973</v>
       </c>
-      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -3034,7 +2815,6 @@
       <c r="C216" t="n">
         <v>6.735713958740234</v>
       </c>
-      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -3046,7 +2826,6 @@
       <c r="C217" t="n">
         <v>6.494999885559082</v>
       </c>
-      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -3058,7 +2837,6 @@
       <c r="C218" t="n">
         <v>7.116786003112793</v>
       </c>
-      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -3070,7 +2848,6 @@
       <c r="C219" t="n">
         <v>4.865714073181152</v>
       </c>
-      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -3082,7 +2859,6 @@
       <c r="C220" t="n">
         <v>4.444285869598389</v>
       </c>
-      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -3094,7 +2870,6 @@
       <c r="C221" t="n">
         <v>5.224999904632568</v>
       </c>
-      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -3106,7 +2881,6 @@
       <c r="C222" t="n">
         <v>6.248570919036865</v>
       </c>
-      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -3118,7 +2892,6 @@
       <c r="C223" t="n">
         <v>6.735713958740234</v>
       </c>
-      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -3130,7 +2903,6 @@
       <c r="C224" t="n">
         <v>5.865356922149658</v>
       </c>
-      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -3142,7 +2914,6 @@
       <c r="C225" t="n">
         <v>5.710713863372803</v>
       </c>
-      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -3154,7 +2925,6 @@
       <c r="C226" t="n">
         <v>6.157143115997314</v>
       </c>
-      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -3166,7 +2936,6 @@
       <c r="C227" t="n">
         <v>3.997143030166626</v>
       </c>
-      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -3178,7 +2947,6 @@
       <c r="C228" t="n">
         <v>3.783214092254639</v>
       </c>
-      <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -3190,7 +2958,6 @@
       <c r="C229" t="n">
         <v>3.260714054107666</v>
       </c>
-      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -3202,7 +2969,6 @@
       <c r="C230" t="n">
         <v>3.067142963409424</v>
       </c>
-      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -3214,7 +2980,6 @@
       <c r="C231" t="n">
         <v>3.182142972946167</v>
       </c>
-      <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -3226,7 +2991,6 @@
       <c r="C232" t="n">
         <v>3.147142887115479</v>
       </c>
-      <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -3238,7 +3002,6 @@
       <c r="C233" t="n">
         <v>3.717499971389771</v>
       </c>
-      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -3250,7 +3013,6 @@
       <c r="C234" t="n">
         <v>4.492856979370117</v>
       </c>
-      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -3262,7 +3024,6 @@
       <c r="C235" t="n">
         <v>4.873929023742676</v>
       </c>
-      <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -3274,7 +3035,6 @@
       <c r="C236" t="n">
         <v>5.125</v>
       </c>
-      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -3286,7 +3046,6 @@
       <c r="C237" t="n">
         <v>5.900356769561768</v>
       </c>
-      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -3298,7 +3057,6 @@
       <c r="C238" t="n">
         <v>5.999642848968506</v>
       </c>
-      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -3310,7 +3068,6 @@
       <c r="C239" t="n">
         <v>6.619643211364746</v>
       </c>
-      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -3322,7 +3079,6 @@
       <c r="C240" t="n">
         <v>6.778571128845215</v>
       </c>
-      <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -3334,7 +3090,6 @@
       <c r="C241" t="n">
         <v>7.222856998443604</v>
       </c>
-      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -3346,7 +3101,6 @@
       <c r="C242" t="n">
         <v>7.622499942779541</v>
       </c>
-      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -3358,7 +3112,6 @@
       <c r="C243" t="n">
         <v>6.870357036590576</v>
       </c>
-      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -3370,7 +3123,6 @@
       <c r="C244" t="n">
         <v>7.348214149475098</v>
       </c>
-      <c r="D244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -3382,7 +3134,6 @@
       <c r="C245" t="n">
         <v>8.478928565979004</v>
       </c>
-      <c r="D245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -3394,7 +3145,6 @@
       <c r="C246" t="n">
         <v>9.422857284545898</v>
       </c>
-      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -3406,9 +3156,6 @@
       <c r="C247" t="n">
         <v>9.274642944335938</v>
       </c>
-      <c r="D247" t="n">
-        <v>1.266667008399963</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -3420,9 +3167,6 @@
       <c r="C248" t="n">
         <v>9.08214282989502</v>
       </c>
-      <c r="D248" t="n">
-        <v>1.666666984558105</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -3434,9 +3178,6 @@
       <c r="C249" t="n">
         <v>9.30142879486084</v>
       </c>
-      <c r="D249" t="n">
-        <v>1.366667032241821</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -3448,9 +3189,6 @@
       <c r="C250" t="n">
         <v>8.838213920593262</v>
       </c>
-      <c r="D250" t="n">
-        <v>1.307999968528748</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -3462,9 +3200,6 @@
       <c r="C251" t="n">
         <v>10.21964263916016</v>
       </c>
-      <c r="D251" t="n">
-        <v>1.379333019256592</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -3476,9 +3211,6 @@
       <c r="C252" t="n">
         <v>10.79357147216797</v>
       </c>
-      <c r="D252" t="n">
-        <v>1.462666988372803</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -3490,9 +3222,6 @@
       <c r="C253" t="n">
         <v>11.25964260101318</v>
       </c>
-      <c r="D253" t="n">
-        <v>2.391333103179932</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -3504,9 +3233,6 @@
       <c r="C254" t="n">
         <v>11.63000011444092</v>
       </c>
-      <c r="D254" t="n">
-        <v>1.789332985877991</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -3518,9 +3244,6 @@
       <c r="C255" t="n">
         <v>12.18928623199463</v>
       </c>
-      <c r="D255" t="n">
-        <v>1.620666980743408</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -3532,9 +3255,6 @@
       <c r="C256" t="n">
         <v>12.69535732269287</v>
       </c>
-      <c r="D256" t="n">
-        <v>1.603332996368408</v>
-      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -3546,9 +3266,6 @@
       <c r="C257" t="n">
         <v>12.53964328765869</v>
       </c>
-      <c r="D257" t="n">
-        <v>1.830000042915344</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -3560,9 +3277,6 @@
       <c r="C258" t="n">
         <v>12.49071407318115</v>
       </c>
-      <c r="D258" t="n">
-        <v>1.840000033378601</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -3574,9 +3288,6 @@
       <c r="C259" t="n">
         <v>12.45964336395264</v>
       </c>
-      <c r="D259" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -3588,9 +3299,6 @@
       <c r="C260" t="n">
         <v>11.99821376800537</v>
       </c>
-      <c r="D260" t="n">
-        <v>1.937999963760376</v>
-      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -3602,9 +3310,6 @@
       <c r="C261" t="n">
         <v>14.20642852783203</v>
       </c>
-      <c r="D261" t="n">
-        <v>1.911332964897156</v>
-      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -3616,9 +3321,6 @@
       <c r="C262" t="n">
         <v>13.77928638458252</v>
       </c>
-      <c r="D262" t="n">
-        <v>1.644000053405762</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -3630,9 +3332,6 @@
       <c r="C263" t="n">
         <v>13.58464336395264</v>
       </c>
-      <c r="D263" t="n">
-        <v>1.663333058357239</v>
-      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -3644,9 +3343,6 @@
       <c r="C264" t="n">
         <v>14.19321441650391</v>
       </c>
-      <c r="D264" t="n">
-        <v>1.892667055130005</v>
-      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -3658,9 +3354,6 @@
       <c r="C265" t="n">
         <v>13.66214275360107</v>
       </c>
-      <c r="D265" t="n">
-        <v>2.171333074569702</v>
-      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -3672,9 +3365,6 @@
       <c r="C266" t="n">
         <v>14.62142944335938</v>
       </c>
-      <c r="D266" t="n">
-        <v>1.929332971572876</v>
-      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -3686,9 +3376,6 @@
       <c r="C267" t="n">
         <v>16.37178611755371</v>
       </c>
-      <c r="D267" t="n">
-        <v>1.937999963760376</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -3700,9 +3387,6 @@
       <c r="C268" t="n">
         <v>19.57749938964844</v>
       </c>
-      <c r="D268" t="n">
-        <v>2.233999967575073</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -3714,9 +3398,6 @@
       <c r="C269" t="n">
         <v>21.49392890930176</v>
       </c>
-      <c r="D269" t="n">
-        <v>2.488667011260986</v>
-      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -3728,9 +3409,6 @@
       <c r="C270" t="n">
         <v>20.88928604125977</v>
       </c>
-      <c r="D270" t="n">
-        <v>2.208667039871216</v>
-      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -3742,9 +3420,6 @@
       <c r="C271" t="n">
         <v>20.3271427154541</v>
       </c>
-      <c r="D271" t="n">
-        <v>1.901999950408936</v>
-      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -3756,9 +3431,6 @@
       <c r="C272" t="n">
         <v>20.88321495056152</v>
       </c>
-      <c r="D272" t="n">
-        <v>2.089999914169312</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -3770,9 +3442,6 @@
       <c r="C273" t="n">
         <v>21.99678611755371</v>
       </c>
-      <c r="D273" t="n">
-        <v>1.866000056266785</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -3784,9 +3453,6 @@
       <c r="C274" t="n">
         <v>23.77714347839355</v>
       </c>
-      <c r="D274" t="n">
-        <v>1.901332974433899</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -3798,9 +3464,6 @@
       <c r="C275" t="n">
         <v>23.96999931335449</v>
       </c>
-      <c r="D275" t="n">
-        <v>1.966667056083679</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -3812,9 +3475,6 @@
       <c r="C276" t="n">
         <v>21.36499977111816</v>
       </c>
-      <c r="D276" t="n">
-        <v>1.883332967758179</v>
-      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -3826,9 +3486,6 @@
       <c r="C277" t="n">
         <v>21.20178604125977</v>
       </c>
-      <c r="D277" t="n">
-        <v>2.259332895278931</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -3840,9 +3497,6 @@
       <c r="C278" t="n">
         <v>19.7792854309082</v>
       </c>
-      <c r="D278" t="n">
-        <v>2.333333015441895</v>
-      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -3854,9 +3508,6 @@
       <c r="C279" t="n">
         <v>16.39678573608398</v>
       </c>
-      <c r="D279" t="n">
-        <v>2.54466700553894</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -3868,9 +3519,6 @@
       <c r="C280" t="n">
         <v>15.64285659790039</v>
       </c>
-      <c r="D280" t="n">
-        <v>2.333333015441895</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -3882,9 +3530,6 @@
       <c r="C281" t="n">
         <v>15.78214263916016</v>
       </c>
-      <c r="D281" t="n">
-        <v>2.823999881744385</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -3896,9 +3541,6 @@
       <c r="C282" t="n">
         <v>15.87357139587402</v>
       </c>
-      <c r="D282" t="n">
-        <v>3.732666969299316</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -3910,9 +3552,6 @@
       <c r="C283" t="n">
         <v>16.09749984741211</v>
       </c>
-      <c r="D283" t="n">
-        <v>6.507999897003174</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -3924,9 +3563,6 @@
       <c r="C284" t="n">
         <v>14.38178634643555</v>
       </c>
-      <c r="D284" t="n">
-        <v>7.290667057037354</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -3938,9 +3574,6 @@
       <c r="C285" t="n">
         <v>16.27678680419922</v>
       </c>
-      <c r="D285" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -3952,9 +3585,6 @@
       <c r="C286" t="n">
         <v>17.61071395874023</v>
       </c>
-      <c r="D286" t="n">
-        <v>11.5600004196167</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -3966,9 +3596,6 @@
       <c r="C287" t="n">
         <v>17.08749961853027</v>
       </c>
-      <c r="D287" t="n">
-        <v>12.93066692352295</v>
-      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -3980,9 +3607,6 @@
       <c r="C288" t="n">
         <v>18.71500015258789</v>
       </c>
-      <c r="D288" t="n">
-        <v>10.86666679382324</v>
-      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -3994,9 +3618,6 @@
       <c r="C289" t="n">
         <v>19.9285717010498</v>
       </c>
-      <c r="D289" t="n">
-        <v>8.423333168029785</v>
-      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -4008,9 +3629,6 @@
       <c r="C290" t="n">
         <v>19.8457145690918</v>
       </c>
-      <c r="D290" t="n">
-        <v>9.986666679382324</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -4022,9 +3640,6 @@
       <c r="C291" t="n">
         <v>17.95035743713379</v>
       </c>
-      <c r="D291" t="n">
-        <v>12.19266700744629</v>
-      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -4036,9 +3651,6 @@
       <c r="C292" t="n">
         <v>18.69357109069824</v>
       </c>
-      <c r="D292" t="n">
-        <v>15.81733322143555</v>
-      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -4050,9 +3662,6 @@
       <c r="C293" t="n">
         <v>19.20571327209473</v>
       </c>
-      <c r="D293" t="n">
-        <v>13.93466663360596</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -4064,9 +3673,6 @@
       <c r="C294" t="n">
         <v>21.14285659790039</v>
       </c>
-      <c r="D294" t="n">
-        <v>13.80533313751221</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -4078,9 +3684,6 @@
       <c r="C295" t="n">
         <v>22.64142990112305</v>
       </c>
-      <c r="D295" t="n">
-        <v>13.82199954986572</v>
-      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -4092,9 +3695,6 @@
       <c r="C296" t="n">
         <v>23.3799991607666</v>
       </c>
-      <c r="D296" t="n">
-        <v>16.16399955749512</v>
-      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -4106,9 +3706,6 @@
       <c r="C297" t="n">
         <v>23.72500038146973</v>
       </c>
-      <c r="D297" t="n">
-        <v>15.07266712188721</v>
-      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -4120,9 +3717,6 @@
       <c r="C298" t="n">
         <v>25.76499938964844</v>
       </c>
-      <c r="D298" t="n">
-        <v>18.36666679382324</v>
-      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -4134,9 +3728,6 @@
       <c r="C299" t="n">
         <v>25.14749908447266</v>
       </c>
-      <c r="D299" t="n">
-        <v>16.14666748046875</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -4148,9 +3739,6 @@
       <c r="C300" t="n">
         <v>27.05500030517578</v>
       </c>
-      <c r="D300" t="n">
-        <v>16.20000076293945</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -4162,9 +3750,6 @@
       <c r="C301" t="n">
         <v>29.70249938964844</v>
       </c>
-      <c r="D301" t="n">
-        <v>16.07733345031738</v>
-      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -4176,9 +3761,6 @@
       <c r="C302" t="n">
         <v>27.84749984741211</v>
       </c>
-      <c r="D302" t="n">
-        <v>14.85799980163574</v>
-      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -4190,9 +3772,6 @@
       <c r="C303" t="n">
         <v>29.51250076293945</v>
       </c>
-      <c r="D303" t="n">
-        <v>13.59799957275391</v>
-      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -4204,9 +3783,6 @@
       <c r="C304" t="n">
         <v>32.3125</v>
       </c>
-      <c r="D304" t="n">
-        <v>13.51333332061768</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -4218,9 +3794,6 @@
       <c r="C305" t="n">
         <v>31.20499992370605</v>
       </c>
-      <c r="D305" t="n">
-        <v>12.57999992370605</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -4232,9 +3805,6 @@
       <c r="C306" t="n">
         <v>31.52499961853027</v>
       </c>
-      <c r="D306" t="n">
-        <v>15.32933330535889</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -4246,9 +3816,6 @@
       <c r="C307" t="n">
         <v>32.56999969482422</v>
       </c>
-      <c r="D307" t="n">
-        <v>16.76066780090332</v>
-      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -4260,9 +3827,6 @@
       <c r="C308" t="n">
         <v>31.72500038146973</v>
       </c>
-      <c r="D308" t="n">
-        <v>18.07399940490723</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -4274,9 +3838,6 @@
       <c r="C309" t="n">
         <v>30.375</v>
       </c>
-      <c r="D309" t="n">
-        <v>17.75266647338867</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -4288,9 +3849,6 @@
       <c r="C310" t="n">
         <v>27.53750038146973</v>
       </c>
-      <c r="D310" t="n">
-        <v>16.02266693115234</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -4302,9 +3860,6 @@
       <c r="C311" t="n">
         <v>27.26749992370605</v>
       </c>
-      <c r="D311" t="n">
-        <v>16.50066757202148</v>
-      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -4316,9 +3871,6 @@
       <c r="C312" t="n">
         <v>30.20000076293945</v>
       </c>
-      <c r="D312" t="n">
-        <v>13.92800045013428</v>
-      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -4330,9 +3882,6 @@
       <c r="C313" t="n">
         <v>29.6875</v>
       </c>
-      <c r="D313" t="n">
-        <v>15.4040002822876</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -4344,9 +3893,6 @@
       <c r="C314" t="n">
         <v>25.65250015258789</v>
       </c>
-      <c r="D314" t="n">
-        <v>15.38133335113525</v>
-      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -4358,9 +3904,6 @@
       <c r="C315" t="n">
         <v>24.11750030517578</v>
       </c>
-      <c r="D315" t="n">
-        <v>12.58399963378906</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -4372,9 +3915,6 @@
       <c r="C316" t="n">
         <v>24.41250038146973</v>
       </c>
-      <c r="D316" t="n">
-        <v>12.94999980926514</v>
-      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -4386,9 +3926,6 @@
       <c r="C317" t="n">
         <v>27.19499969482422</v>
       </c>
-      <c r="D317" t="n">
-        <v>16.32200050354004</v>
-      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -4400,9 +3937,6 @@
       <c r="C318" t="n">
         <v>23.49250030517578</v>
       </c>
-      <c r="D318" t="n">
-        <v>16.10000038146973</v>
-      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -4414,9 +3948,6 @@
       <c r="C319" t="n">
         <v>24.7549991607666</v>
       </c>
-      <c r="D319" t="n">
-        <v>14.76533317565918</v>
-      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -4428,9 +3959,6 @@
       <c r="C320" t="n">
         <v>23.87249946594238</v>
       </c>
-      <c r="D320" t="n">
-        <v>13.74266719818115</v>
-      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -4442,9 +3970,6 @@
       <c r="C321" t="n">
         <v>26.10250091552734</v>
       </c>
-      <c r="D321" t="n">
-        <v>15.69999980926514</v>
-      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -4456,9 +3981,6 @@
       <c r="C322" t="n">
         <v>26.53499984741211</v>
       </c>
-      <c r="D322" t="n">
-        <v>13.93400001525879</v>
-      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -4470,9 +3992,6 @@
       <c r="C323" t="n">
         <v>28.17749977111816</v>
       </c>
-      <c r="D323" t="n">
-        <v>14.15333271026611</v>
-      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -4484,9 +4003,6 @@
       <c r="C324" t="n">
         <v>28.36499977111816</v>
       </c>
-      <c r="D324" t="n">
-        <v>13.20266723632812</v>
-      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -4498,9 +4014,6 @@
       <c r="C325" t="n">
         <v>27.59250068664551</v>
       </c>
-      <c r="D325" t="n">
-        <v>12.55000019073486</v>
-      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -4512,9 +4025,6 @@
       <c r="C326" t="n">
         <v>28.95000076293945</v>
       </c>
-      <c r="D326" t="n">
-        <v>14.32400035858154</v>
-      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -4526,9 +4036,6 @@
       <c r="C327" t="n">
         <v>31.75749969482422</v>
       </c>
-      <c r="D327" t="n">
-        <v>16.8700008392334</v>
-      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -4540,9 +4047,6 @@
       <c r="C328" t="n">
         <v>34.47249984741211</v>
       </c>
-      <c r="D328" t="n">
-        <v>16.94533348083496</v>
-      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -4554,9 +4058,6 @@
       <c r="C329" t="n">
         <v>35.9275016784668</v>
       </c>
-      <c r="D329" t="n">
-        <v>19.12666702270508</v>
-      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -4568,9 +4069,6 @@
       <c r="C330" t="n">
         <v>36.27500152587891</v>
       </c>
-      <c r="D330" t="n">
-        <v>20.99200057983398</v>
-      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -4582,9 +4080,6 @@
       <c r="C331" t="n">
         <v>38.29249954223633</v>
       </c>
-      <c r="D331" t="n">
-        <v>22.9333324432373</v>
-      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -4596,9 +4091,6 @@
       <c r="C332" t="n">
         <v>36.22000122070312</v>
       </c>
-      <c r="D332" t="n">
-        <v>24.68266677856445</v>
-      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -4610,9 +4102,6 @@
       <c r="C333" t="n">
         <v>37.27500152587891</v>
       </c>
-      <c r="D333" t="n">
-        <v>21.53333282470703</v>
-      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -4624,9 +4113,6 @@
       <c r="C334" t="n">
         <v>41.20000076293945</v>
       </c>
-      <c r="D334" t="n">
-        <v>23.7413330078125</v>
-      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -4638,9 +4124,6 @@
       <c r="C335" t="n">
         <v>38.56499862670898</v>
       </c>
-      <c r="D335" t="n">
-        <v>22.83466720581055</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -4652,9 +4135,6 @@
       <c r="C336" t="n">
         <v>42.46749877929688</v>
       </c>
-      <c r="D336" t="n">
-        <v>22.14999961853027</v>
-      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -4666,9 +4146,6 @@
       <c r="C337" t="n">
         <v>42.48749923706055</v>
       </c>
-      <c r="D337" t="n">
-        <v>20.36266708374023</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -4680,9 +4157,6 @@
       <c r="C338" t="n">
         <v>42.54000091552734</v>
       </c>
-      <c r="D338" t="n">
-        <v>20.79999923706055</v>
-      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -4694,9 +4168,6 @@
       <c r="C339" t="n">
         <v>41.79249954223633</v>
       </c>
-      <c r="D339" t="n">
-        <v>23.39999961853027</v>
-      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -4708,9 +4179,6 @@
       <c r="C340" t="n">
         <v>44.6349983215332</v>
       </c>
-      <c r="D340" t="n">
-        <v>23.00066757202148</v>
-      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -4722,9 +4190,6 @@
       <c r="C341" t="n">
         <v>41.65999984741211</v>
       </c>
-      <c r="D341" t="n">
-        <v>17.08399963378906</v>
-      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -4736,9 +4201,6 @@
       <c r="C342" t="n">
         <v>41.60250091552734</v>
       </c>
-      <c r="D342" t="n">
-        <v>19.56733322143555</v>
-      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -4750,9 +4212,6 @@
       <c r="C343" t="n">
         <v>46.99750137329102</v>
       </c>
-      <c r="D343" t="n">
-        <v>19.05733299255371</v>
-      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -4764,9 +4223,6 @@
       <c r="C344" t="n">
         <v>45.95500183105469</v>
       </c>
-      <c r="D344" t="n">
-        <v>24.00466728210449</v>
-      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -4778,9 +4234,6 @@
       <c r="C345" t="n">
         <v>49.78250122070312</v>
       </c>
-      <c r="D345" t="n">
-        <v>19.86599922180176</v>
-      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -4792,9 +4245,6 @@
       <c r="C346" t="n">
         <v>57.10250091552734</v>
       </c>
-      <c r="D346" t="n">
-        <v>19.79599952697754</v>
-      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -4806,9 +4256,6 @@
       <c r="C347" t="n">
         <v>56.98749923706055</v>
       </c>
-      <c r="D347" t="n">
-        <v>20.38466644287109</v>
-      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -4820,9 +4267,6 @@
       <c r="C348" t="n">
         <v>54.76250076293945</v>
       </c>
-      <c r="D348" t="n">
-        <v>22.55066680908203</v>
-      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -4834,9 +4278,6 @@
       <c r="C349" t="n">
         <v>46.1150016784668</v>
       </c>
-      <c r="D349" t="n">
-        <v>24</v>
-      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -4848,9 +4289,6 @@
       <c r="C350" t="n">
         <v>38.72249984741211</v>
       </c>
-      <c r="D350" t="n">
-        <v>20.40666770935059</v>
-      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -4862,9 +4300,6 @@
       <c r="C351" t="n">
         <v>41.7400016784668</v>
       </c>
-      <c r="D351" t="n">
-        <v>20.3613338470459</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -4876,9 +4311,6 @@
       <c r="C352" t="n">
         <v>43.56999969482422</v>
       </c>
-      <c r="D352" t="n">
-        <v>20.46266746520996</v>
-      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -4890,9 +4322,6 @@
       <c r="C353" t="n">
         <v>47.90999984741211</v>
       </c>
-      <c r="D353" t="n">
-        <v>18.84133338928223</v>
-      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -4904,9 +4333,6 @@
       <c r="C354" t="n">
         <v>52.47000122070312</v>
       </c>
-      <c r="D354" t="n">
-        <v>15.92333316802979</v>
-      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -4918,9 +4344,6 @@
       <c r="C355" t="n">
         <v>43.90000152587891</v>
       </c>
-      <c r="D355" t="n">
-        <v>12.36733341217041</v>
-      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -4932,9 +4355,6 @@
       <c r="C356" t="n">
         <v>50.79249954223633</v>
       </c>
-      <c r="D356" t="n">
-        <v>15.34733295440674</v>
-      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -4946,9 +4366,6 @@
       <c r="C357" t="n">
         <v>53.47499847412109</v>
       </c>
-      <c r="D357" t="n">
-        <v>16.17666625976562</v>
-      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -4960,9 +4377,6 @@
       <c r="C358" t="n">
         <v>51.60749816894531</v>
       </c>
-      <c r="D358" t="n">
-        <v>14.93866729736328</v>
-      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -4974,9 +4388,6 @@
       <c r="C359" t="n">
         <v>56.26750183105469</v>
       </c>
-      <c r="D359" t="n">
-        <v>16.10000038146973</v>
-      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -4988,9 +4399,6 @@
       <c r="C360" t="n">
         <v>62.3849983215332</v>
       </c>
-      <c r="D360" t="n">
-        <v>21.08799934387207</v>
-      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -5002,9 +4410,6 @@
       <c r="C361" t="n">
         <v>66.81749725341797</v>
       </c>
-      <c r="D361" t="n">
-        <v>21.95999908447266</v>
-      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -5016,9 +4421,6 @@
       <c r="C362" t="n">
         <v>74.05999755859375</v>
       </c>
-      <c r="D362" t="n">
-        <v>28.29999923706055</v>
-      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -5030,9 +4432,6 @@
       <c r="C363" t="n">
         <v>76.07499694824219</v>
       </c>
-      <c r="D363" t="n">
-        <v>44.91266632080078</v>
-      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -5044,9 +4443,6 @@
       <c r="C364" t="n">
         <v>70.56999969482422</v>
       </c>
-      <c r="D364" t="n">
-        <v>47.41733169555664</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -5058,9 +4454,6 @@
       <c r="C365" t="n">
         <v>61.625</v>
       </c>
-      <c r="D365" t="n">
-        <v>33.59999847412109</v>
-      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -5072,9 +4465,6 @@
       <c r="C366" t="n">
         <v>71.5625</v>
       </c>
-      <c r="D366" t="n">
-        <v>50.33333206176758</v>
-      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -5086,9 +4476,6 @@
       <c r="C367" t="n">
         <v>79.4375</v>
       </c>
-      <c r="D367" t="n">
-        <v>57.20000076293945</v>
-      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -5100,9 +4487,6 @@
       <c r="C368" t="n">
         <v>91.27999877929688</v>
       </c>
-      <c r="D368" t="n">
-        <v>72.19999694824219</v>
-      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -5114,9 +4498,6 @@
       <c r="C369" t="n">
         <v>108.1999969482422</v>
       </c>
-      <c r="D369" t="n">
-        <v>96.61333465576172</v>
-      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -5128,9 +4509,6 @@
       <c r="C370" t="n">
         <v>132.7599945068359</v>
       </c>
-      <c r="D370" t="n">
-        <v>167.3800048828125</v>
-      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -5142,9 +4520,6 @@
       <c r="C371" t="n">
         <v>117.6399993896484</v>
       </c>
-      <c r="D371" t="n">
-        <v>146.9199981689453</v>
-      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -5156,9 +4531,6 @@
       <c r="C372" t="n">
         <v>109.1100006103516</v>
       </c>
-      <c r="D372" t="n">
-        <v>131.3333282470703</v>
-      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -5170,9 +4542,6 @@
       <c r="C373" t="n">
         <v>121.0100021362305</v>
       </c>
-      <c r="D373" t="n">
-        <v>199.1966705322266</v>
-      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -5184,9 +4553,6 @@
       <c r="C374" t="n">
         <v>133.5200042724609</v>
       </c>
-      <c r="D374" t="n">
-        <v>239.8200073242188</v>
-      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -5198,9 +4564,6 @@
       <c r="C375" t="n">
         <v>133.75</v>
       </c>
-      <c r="D375" t="n">
-        <v>271.4299926757812</v>
-      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -5212,9 +4575,6 @@
       <c r="C376" t="n">
         <v>123.75</v>
       </c>
-      <c r="D376" t="n">
-        <v>230.0366668701172</v>
-      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -5226,9 +4586,6 @@
       <c r="C377" t="n">
         <v>123.6600036621094</v>
       </c>
-      <c r="D377" t="n">
-        <v>229.4566650390625</v>
-      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -5240,9 +4597,6 @@
       <c r="C378" t="n">
         <v>132.0399932861328</v>
       </c>
-      <c r="D378" t="n">
-        <v>234.6000061035156</v>
-      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -5254,9 +4608,6 @@
       <c r="C379" t="n">
         <v>125.0800018310547</v>
       </c>
-      <c r="D379" t="n">
-        <v>209.2666625976562</v>
-      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -5268,9 +4619,6 @@
       <c r="C380" t="n">
         <v>136.6000061035156</v>
       </c>
-      <c r="D380" t="n">
-        <v>227.9733276367188</v>
-      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -5282,9 +4630,6 @@
       <c r="C381" t="n">
         <v>146.3600006103516</v>
       </c>
-      <c r="D381" t="n">
-        <v>233.3333282470703</v>
-      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -5296,9 +4641,6 @@
       <c r="C382" t="n">
         <v>152.8300018310547</v>
       </c>
-      <c r="D382" t="n">
-        <v>244.6933288574219</v>
-      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -5310,9 +4652,6 @@
       <c r="C383" t="n">
         <v>141.8999938964844</v>
       </c>
-      <c r="D383" t="n">
-        <v>259.4666748046875</v>
-      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -5324,9 +4663,6 @@
       <c r="C384" t="n">
         <v>148.9900054931641</v>
       </c>
-      <c r="D384" t="n">
-        <v>381.6666564941406</v>
-      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -5338,9 +4674,6 @@
       <c r="C385" t="n">
         <v>167.4799957275391</v>
       </c>
-      <c r="D385" t="n">
-        <v>386.8999938964844</v>
-      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -5352,9 +4685,6 @@
       <c r="C386" t="n">
         <v>177.8300018310547</v>
       </c>
-      <c r="D386" t="n">
-        <v>382.5833435058594</v>
-      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -5366,9 +4696,6 @@
       <c r="C387" t="n">
         <v>174.0099945068359</v>
       </c>
-      <c r="D387" t="n">
-        <v>311.7366638183594</v>
-      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -5380,9 +4707,6 @@
       <c r="C388" t="n">
         <v>164.6999969482422</v>
       </c>
-      <c r="D388" t="n">
-        <v>289.8933410644531</v>
-      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -5394,9 +4718,6 @@
       <c r="C389" t="n">
         <v>174.0299987792969</v>
       </c>
-      <c r="D389" t="n">
-        <v>360.3833312988281</v>
-      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -5408,9 +4729,6 @@
       <c r="C390" t="n">
         <v>156.7100067138672</v>
       </c>
-      <c r="D390" t="n">
-        <v>286.92333984375</v>
-      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -5422,9 +4740,6 @@
       <c r="C391" t="n">
         <v>149.8999938964844</v>
       </c>
-      <c r="D391" t="n">
-        <v>251.7200012207031</v>
-      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -5436,9 +4751,6 @@
       <c r="C392" t="n">
         <v>136.0399932861328</v>
       </c>
-      <c r="D392" t="n">
-        <v>227</v>
-      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -5450,9 +4762,6 @@
       <c r="C393" t="n">
         <v>161.0099945068359</v>
       </c>
-      <c r="D393" t="n">
-        <v>301.2766723632812</v>
-      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -5464,9 +4773,6 @@
       <c r="C394" t="n">
         <v>156.6399993896484</v>
       </c>
-      <c r="D394" t="n">
-        <v>272.5799865722656</v>
-      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -5478,9 +4784,6 @@
       <c r="C395" t="n">
         <v>138.2100067138672</v>
       </c>
-      <c r="D395" t="n">
-        <v>254.5</v>
-      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -5492,9 +4795,6 @@
       <c r="C396" t="n">
         <v>155.0800018310547</v>
       </c>
-      <c r="D396" t="n">
-        <v>234.0500030517578</v>
-      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -5506,9 +4806,6 @@
       <c r="C397" t="n">
         <v>148.2100067138672</v>
       </c>
-      <c r="D397" t="n">
-        <v>197.0800018310547</v>
-      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -5520,9 +4817,6 @@
       <c r="C398" t="n">
         <v>130.2799987792969</v>
       </c>
-      <c r="D398" t="n">
-        <v>118.4700012207031</v>
-      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -5534,9 +4828,6 @@
       <c r="C399" t="n">
         <v>143.9700012207031</v>
       </c>
-      <c r="D399" t="n">
-        <v>173.8899993896484</v>
-      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -5548,9 +4839,6 @@
       <c r="C400" t="n">
         <v>146.8300018310547</v>
       </c>
-      <c r="D400" t="n">
-        <v>206.2100067138672</v>
-      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -5562,9 +4850,6 @@
       <c r="C401" t="n">
         <v>164.2700042724609</v>
       </c>
-      <c r="D401" t="n">
-        <v>199.9100036621094</v>
-      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -5576,9 +4861,6 @@
       <c r="C402" t="n">
         <v>169.2799987792969</v>
       </c>
-      <c r="D402" t="n">
-        <v>163.1699981689453</v>
-      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -5590,9 +4872,6 @@
       <c r="C403" t="n">
         <v>177.6999969482422</v>
       </c>
-      <c r="D403" t="n">
-        <v>202.5899963378906</v>
-      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -5604,9 +4883,6 @@
       <c r="C404" t="n">
         <v>193.7799987792969</v>
       </c>
-      <c r="D404" t="n">
-        <v>276.489990234375</v>
-      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -5618,9 +4894,6 @@
       <c r="C405" t="n">
         <v>196.2400054931641</v>
       </c>
-      <c r="D405" t="n">
-        <v>266.260009765625</v>
-      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -5632,9 +4905,6 @@
       <c r="C406" t="n">
         <v>189.4900054931641</v>
       </c>
-      <c r="D406" t="n">
-        <v>257.260009765625</v>
-      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -5646,9 +4916,6 @@
       <c r="C407" t="n">
         <v>171.2200012207031</v>
       </c>
-      <c r="D407" t="n">
-        <v>244.8099975585938</v>
-      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -5660,9 +4927,6 @@
       <c r="C408" t="n">
         <v>171</v>
       </c>
-      <c r="D408" t="n">
-        <v>204.0399932861328</v>
-      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -5674,9 +4938,6 @@
       <c r="C409" t="n">
         <v>190.3300018310547</v>
       </c>
-      <c r="D409" t="n">
-        <v>233.1399993896484</v>
-      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -5688,9 +4949,6 @@
       <c r="C410" t="n">
         <v>187.1499938964844</v>
       </c>
-      <c r="D410" t="n">
-        <v>250.0800018310547</v>
-      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -5702,9 +4960,6 @@
       <c r="C411" t="n">
         <v>183.9900054931641</v>
       </c>
-      <c r="D411" t="n">
-        <v>188.5</v>
-      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -5716,9 +4971,6 @@
       <c r="C412" t="n">
         <v>179.5500030517578</v>
       </c>
-      <c r="D412" t="n">
-        <v>200.5200042724609</v>
-      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -5730,9 +4982,6 @@
       <c r="C413" t="n">
         <v>171.1900024414062</v>
       </c>
-      <c r="D413" t="n">
-        <v>176.1699981689453</v>
-      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -5744,9 +4993,6 @@
       <c r="C414" t="n">
         <v>169.5800018310547</v>
       </c>
-      <c r="D414" t="n">
-        <v>182</v>
-      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -5758,9 +5004,6 @@
       <c r="C415" t="n">
         <v>192.8999938964844</v>
       </c>
-      <c r="D415" t="n">
-        <v>178.1300048828125</v>
-      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -5772,9 +5015,6 @@
       <c r="C416" t="n">
         <v>212.0899963378906</v>
       </c>
-      <c r="D416" t="n">
-        <v>201.0200042724609</v>
-      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -5786,9 +5026,6 @@
       <c r="C417" t="n">
         <v>224.3699951171875</v>
       </c>
-      <c r="D417" t="n">
-        <v>227.6900024414062</v>
-      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -5800,9 +5037,6 @@
       <c r="C418" t="n">
         <v>228.5500030517578</v>
       </c>
-      <c r="D418" t="n">
-        <v>215.2599945068359</v>
-      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -5814,9 +5048,6 @@
       <c r="C419" t="n">
         <v>229.5200042724609</v>
       </c>
-      <c r="D419" t="n">
-        <v>262.6700134277344</v>
-      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -5828,9 +5059,6 @@
       <c r="C420" t="n">
         <v>220.9700012207031</v>
       </c>
-      <c r="D420" t="n">
-        <v>252.0399932861328</v>
-      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -5842,9 +5070,6 @@
       <c r="C421" t="n">
         <v>237.2700042724609</v>
       </c>
-      <c r="D421" t="n">
-        <v>352.3800048828125</v>
-      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -5856,9 +5081,6 @@
       <c r="C422" t="n">
         <v>248.9299926757812</v>
       </c>
-      <c r="D422" t="n">
-        <v>390.1000061035156</v>
-      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -5870,9 +5092,6 @@
       <c r="C423" t="n">
         <v>229.9900054931641</v>
       </c>
-      <c r="D423" t="n">
-        <v>386.6799926757812</v>
-      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -5884,8 +5103,16 @@
       <c r="C424" t="n">
         <v>241.7899932861328</v>
       </c>
-      <c r="D424" t="n">
-        <v>300.3399963378906</v>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B425" t="n">
+        <v>374.6499938964844</v>
+      </c>
+      <c r="C425" t="n">
+        <v>219.8099975585938</v>
       </c>
     </row>
   </sheetData>
